--- a/testakten/sozialrecht-rollstuhl-tannenberg/03-margarete-pflegegrad/Pflegetagebuch_Margarete_Februar_2026.xlsx
+++ b/testakten/sozialrecht-rollstuhl-tannenberg/03-margarete-pflegegrad/Pflegetagebuch_Margarete_Februar_2026.xlsx
@@ -478,10 +478,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gefuehrt von Schwiegertochter Bertha Tannenberg - Zeitraum 01.02.2026 bis 28.02.2026</t>
-        </is>
-      </c>
-    </row>
+          <t>Geführt von Schwiegertochter Bertha Tannenberg - Zeitraum 01.02.2026 bis 28.02.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -495,7 +496,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Taetigkeit</t>
+          <t>Tätigkeit</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -505,12 +506,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Haeufigkeit/Tag</t>
+          <t>Häufigkeit/Tag</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Selbstaendigkeit</t>
+          <t>Selbstständigkeit</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -548,12 +549,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Sturz vermieden, Bertha hat gefuehrt</t>
+          <t>Sturz vermieden, Bertha hat geführt</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -586,12 +587,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Knoepfe nicht moeglich, Reissverschluss nicht moeglich</t>
+          <t>Knöpfe nicht möglich, Reißverschluss nicht möglich</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -624,7 +625,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend selbstaendig</t>
+          <t>überwiegend selbstständig</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -658,7 +659,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -685,7 +686,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Mahlzeitenzubereitung Fruehstueck</t>
+          <t>Mahlzeitenzubereitung Frühstück</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -696,7 +697,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -723,7 +724,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Naechtliche Unruhe und Rufen</t>
+          <t>Nächtliche Unruhe und Rufen</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -734,7 +735,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>eingeschraenkt</t>
+          <t>eingeschränkt</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -772,7 +773,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -799,7 +800,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Waschung Unterkoerper</t>
+          <t>Waschung Unterkörper</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -810,7 +811,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -844,12 +845,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>unmoeglich ohne Hilfe zweier Personen</t>
+          <t>unmöglich ohne Hilfe zweier Personen</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Termin Hausarzt; Olaf hat zusaetzlich gestuetzt</t>
+          <t>Termin Hausarzt; Olaf hat zusätzlich gestützt</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -882,12 +883,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>unselbstaendig</t>
+          <t>unselbstständig</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Wochendispenser gefuellt durch Bertha, Mandantin nimmt aus Dispenser</t>
+          <t>Wochendispenser gefüllt durch Bertha, Mandantin nimmt aus Dispenser</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -909,7 +910,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Toilettengang tagsueber</t>
+          <t>Toilettengang tagsüber</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -920,12 +921,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Hose oeffnen, hinsetzen, reinigen alle nicht selbstaendig</t>
+          <t>Hose öffnen, hinsetzen, reinigen alle nicht selbstständig</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -947,7 +948,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Wahnhafte Aeusserungen</t>
+          <t>Wahnhafte Äußerungen</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -958,7 +959,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>eingeschraenkt</t>
+          <t>eingeschränkt</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -996,7 +997,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1030,7 +1031,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1064,7 +1065,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend selbstaendig</t>
+          <t>überwiegend selbstständig</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1098,12 +1099,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Sehr langsames Essen, oft muss Bertha fuettern</t>
+          <t>Sehr langsames Essen, oft muss Bertha füttern</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1136,7 +1137,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>eingeschraenkt</t>
+          <t>eingeschränkt</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1174,7 +1175,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1201,7 +1202,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Waschung Oberkoerper</t>
+          <t>Waschung Oberkörper</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1246,7 +1247,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend selbstaendig</t>
+          <t>überwiegend selbstständig</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1269,7 +1270,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Inkontinenzversorgung tagsueber</t>
+          <t>Inkontinenzversorgung tagsüber</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1280,7 +1281,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1318,7 +1319,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1345,7 +1346,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Naechtliche Unruhe</t>
+          <t>Nächtliche Unruhe</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1356,7 +1357,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>eingeschraenkt</t>
+          <t>eingeschränkt</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1379,7 +1380,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Wundversorgung kleine Hautlaesion li Knoechel</t>
+          <t>Wundversorgung kleine Hautläsion li Knöchel</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1390,7 +1391,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>unselbstaendig</t>
+          <t>unselbstständig</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1428,7 +1429,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1466,7 +1467,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -1504,7 +1505,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -1538,7 +1539,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>unselbstaendig</t>
+          <t>unselbstständig</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -1576,7 +1577,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
@@ -1610,7 +1611,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>ueberwiegend unselbstaendig</t>
+          <t>überwiegend unselbstständig</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr"/>
@@ -1633,7 +1634,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Naechtliche Unruhe</t>
+          <t>Nächtliche Unruhe</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -1644,7 +1645,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>eingeschraenkt</t>
+          <t>eingeschränkt</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
@@ -1678,7 +1679,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>vollstaendig unselbstaendig</t>
+          <t>vollständig unselbstständig</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
@@ -1688,6 +1689,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -1705,14 +1707,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Naechtliche Unruhe in ca. 12 von 28 Tagen mit Dauer 25-50 Minuten.</t>
+          <t>Nächtliche Unruhe in ca. 12 von 28 Tagen mit Dauer 25-50 Minuten.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Beinahe-Sturz in der Dusche am 21.02.2026 belegt erhoehte Selbstgefaehrdung.</t>
+          <t>Beinahe-Sturz in der Dusche am 21.02.2026 belegt erhöhte Selbstgefährdung.</t>
         </is>
       </c>
     </row>
